--- a/docs/Internship_artifacts/Agile_Template_v0.1.xlsx
+++ b/docs/Internship_artifacts/Agile_Template_v0.1.xlsx
@@ -4,7 +4,7 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="0"/>
   <workbookProtection lockStructure="0" lockWindows="0" workbookPassword="0000"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="1" state="visible" r:id="rId2"/>
@@ -457,7 +457,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t xml:space="preserve">Planned Sprint</t>
   </si>
@@ -585,7 +585,7 @@
     <t>US-11</t>
   </si>
   <si>
-    <t xml:space="preserve">changes made in UI for batter UX, and add MD (markfile) upload ad understanding</t>
+    <t xml:space="preserve">as user for batter ux changes made in UI and add MD (markfile) upload and understanding.</t>
   </si>
   <si>
     <t xml:space="preserve">US-01 to US-10</t>
@@ -597,10 +597,25 @@
     <t>US-12</t>
   </si>
   <si>
-    <t>deployment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-01 &amp; US-11</t>
+    <t xml:space="preserve">add clear chat button so that use can clear the chat and auto scrolling to lates chat for ease of uges, and as a use i want to swich automatically to a new model if old models limite is exceed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-01 to US-11</t>
+  </si>
+  <si>
+    <t>US-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">as a use i want creator information, so that i can contact them if need.</t>
+  </si>
+  <si>
+    <t>US-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deployment on streamlit cloud, connect qdrant cloud for 24/7 uptime and perestiance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-01 &amp; US-13</t>
   </si>
   <si>
     <t xml:space="preserve">NOTES:  Task sizing should be between 0.5 to 12 hours</t>
@@ -762,7 +777,7 @@
     <numFmt numFmtId="168" formatCode="[$-1009]d\-mmm\-yy;@"/>
     <numFmt numFmtId="169" formatCode="dd-mmm-yy"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="10.000000"/>
       <color theme="1"/>
@@ -903,6 +918,11 @@
     </font>
     <font>
       <sz val="11.000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1515,7 +1535,7 @@
     <xf fontId="19" fillId="0" borderId="9" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="20" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1533,38 +1553,42 @@
     <xf fontId="22" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="23" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="23" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="23" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="24" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="24" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="14" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="23" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf fontId="25" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="24" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf fontId="23" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="24" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="23" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="24" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="23" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="24" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="23" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="24" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="23" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="24" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1577,44 +1601,44 @@
     <xf fontId="14" fillId="34" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="26" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="26" fillId="35" borderId="14" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="27" fillId="35" borderId="14" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="26" fillId="35" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="27" fillId="35" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="26" fillId="35" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="27" fillId="35" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="26" fillId="35" borderId="11" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="27" fillId="35" borderId="11" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="26" fillId="35" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="27" fillId="35" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="26" fillId="35" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="27" fillId="35" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="26" fillId="35" borderId="17" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="27" fillId="35" borderId="17" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="26" fillId="35" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="27" fillId="35" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="26" fillId="35" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="27" fillId="35" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="26" fillId="35" borderId="19" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="27" fillId="35" borderId="19" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="26" fillId="36" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="27" fillId="36" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="27" fillId="37" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="28" fillId="37" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="14" fillId="0" borderId="0" numFmtId="0" xfId="45" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1629,7 +1653,7 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="23" fillId="0" borderId="21" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="24" fillId="0" borderId="21" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1641,7 +1665,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="24" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="25" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1689,10 +1713,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf fontId="28" fillId="38" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="29" fillId="38" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="29" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="30" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="14" fillId="0" borderId="10" numFmtId="0" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1709,7 +1733,7 @@
     <xf fontId="14" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="29" fillId="39" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="30" fillId="39" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="14" fillId="0" borderId="10" numFmtId="0" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1730,10 +1754,10 @@
     <xf fontId="14" fillId="0" borderId="10" numFmtId="169" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="30" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="31" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="31" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="32" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1805,7 +1829,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Sumeet Kumar Barua08" id="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}"/>
+  <person displayName="Sumeet Kumar Barua08" id="{E342A5D8-9227-19F5-C930-935878CACE1A}"/>
 </personList>
 </file>
 
@@ -2314,7 +2338,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="F1" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{00AF0084-0059-46C3-AA99-008E004D0035}" done="0">
+  <threadedComment ref="F1" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00AF0084-0059-46C3-AA99-008E004D0035}" done="0">
     <text xml:space="preserve">Mention the US ID(s) on which the user story depends.
 </text>
   </threadedComment>
@@ -2323,75 +2347,75 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D2" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{00F800F9-00F5-4EEB-A626-00AC003800DC}" done="0">
+  <threadedComment ref="D2" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00F800F9-00F5-4EEB-A626-00AC003800DC}" done="0">
     <text xml:space="preserve">Please enter the dates in either of these formats: 
 9/15/2016  or
 15-Sep-2016
 </text>
   </threadedComment>
-  <threadedComment ref="E2" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{000200F9-001E-4BFA-B542-00FB000F008B}" done="0">
+  <threadedComment ref="E2" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{000200F9-001E-4BFA-B542-00FB000F008B}" done="0">
     <text xml:space="preserve">Please enter the dates in either of these formats: 
 9/15/2016  or
 15-Sep-2016
 </text>
   </threadedComment>
-  <threadedComment ref="K3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{00A900BC-0098-4ADA-991F-004100B900CA}" done="0">
+  <threadedComment ref="K3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00A900BC-0098-4ADA-991F-004100B900CA}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 2 work
 </text>
   </threadedComment>
-  <threadedComment ref="L3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{007E003B-0039-4F19-8B63-00C500F60085}" done="0">
+  <threadedComment ref="L3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{007E003B-0039-4F19-8B63-00C500F60085}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 3 work
 </text>
   </threadedComment>
-  <threadedComment ref="M3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{004500B6-006E-4D69-9AA8-00D500D5008B}" done="0">
+  <threadedComment ref="M3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{004500B6-006E-4D69-9AA8-00D500D5008B}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 4 work
 </text>
   </threadedComment>
-  <threadedComment ref="N3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{0076002F-00B4-461E-96FC-0042003D000F}" done="0">
+  <threadedComment ref="N3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{0076002F-00B4-461E-96FC-0042003D000F}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 5 work
 </text>
   </threadedComment>
-  <threadedComment ref="O3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{00BD00ED-0020-4FB3-8E63-00DF0065002A}" done="0">
+  <threadedComment ref="O3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00BD00ED-0020-4FB3-8E63-00DF0065002A}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 6 work
 </text>
   </threadedComment>
-  <threadedComment ref="P3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{007A00FA-00D7-4145-9950-0006005B0057}" done="0">
+  <threadedComment ref="P3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{007A00FA-00D7-4145-9950-0006005B0057}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 7 work
 </text>
   </threadedComment>
-  <threadedComment ref="Q3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{004100A5-0097-4D17-B730-0012008100F5}" done="0">
+  <threadedComment ref="Q3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{004100A5-0097-4D17-B730-0012008100F5}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 8 work
 </text>
   </threadedComment>
-  <threadedComment ref="R3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{005B0000-002C-4B0C-BADE-00E6000B00C9}" done="0">
+  <threadedComment ref="R3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{005B0000-002C-4B0C-BADE-00E6000B00C9}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 9 work
 </text>
   </threadedComment>
-  <threadedComment ref="S3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{00430062-00FB-4330-872F-006500830079}" done="0">
+  <threadedComment ref="S3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00430062-00FB-4330-872F-006500830079}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 10 work
 </text>
   </threadedComment>
-  <threadedComment ref="T3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{002900E7-007B-4830-9B69-00F800460012}" done="0">
+  <threadedComment ref="T3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{002900E7-007B-4830-9B69-00F800460012}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 11 work
 </text>
   </threadedComment>
-  <threadedComment ref="U3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{007300EB-00B7-41DD-AFC5-000B00040082}" done="0">
+  <threadedComment ref="U3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{007300EB-00B7-41DD-AFC5-000B00040082}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 12 work
 </text>
   </threadedComment>
-  <threadedComment ref="V3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{00370093-00CE-47AD-A1F0-00900043001F}" done="0">
+  <threadedComment ref="V3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00370093-00CE-47AD-A1F0-00900043001F}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 13 work
 </text>
   </threadedComment>
-  <threadedComment ref="W3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{00C30045-0073-4B39-B18E-007A00DC001F}" done="0">
+  <threadedComment ref="W3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00C30045-0073-4B39-B18E-007A00DC001F}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 14 work
 </text>
   </threadedComment>
-  <threadedComment ref="I3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{0015002A-006D-42C0-8CB5-0043007D001D}" done="0">
+  <threadedComment ref="I3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{0015002A-006D-42C0-8CB5-0043007D001D}" done="0">
     <text xml:space="preserve">This is the total task estimated in hours for all the user stories 
 </text>
   </threadedComment>
-  <threadedComment ref="J3" personId="{7B7169D9-92FB-D66D-B64D-8A2E0EBFE9E3}" id="{006300B3-0017-43A3-AC6F-00670025009B}" done="0">
+  <threadedComment ref="J3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{006300B3-0017-43A3-AC6F-00670025009B}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 1 work
 </text>
   </threadedComment>
@@ -2409,7 +2433,7 @@
     <col customWidth="1" min="1" max="1" width="6.8867200000000004"/>
     <col customWidth="1" min="2" max="2" width="6.6640600000000001"/>
     <col customWidth="1" min="3" max="3" style="1" width="7.8867200000000004"/>
-    <col customWidth="1" min="4" max="4" style="1" width="139.441"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" style="1" width="226.11328125"/>
     <col customWidth="1" min="5" max="5" width="13.886699999999999"/>
     <col customWidth="1" min="6" max="6" width="9.4414099999999994"/>
     <col customWidth="1" min="7" max="7" width="8.7773400000000006"/>
@@ -2702,7 +2726,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" ht="27.600000000000001">
+    <row r="12" ht="28.5">
       <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
@@ -2728,7 +2752,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" ht="13.800000000000001">
+    <row r="13" ht="28.5">
       <c r="A13" s="5" t="s">
         <v>44</v>
       </c>
@@ -2738,11 +2762,11 @@
       <c r="C13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="7" t="s">
         <v>46</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>47</v>
@@ -2755,314 +2779,344 @@
       </c>
     </row>
     <row r="14" ht="52.799999999999997" customHeight="1">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" ht="13.199999999999999">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" ht="28.5">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="16" ht="13.199999999999999">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
     </row>
     <row r="17" ht="13.199999999999999">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
     </row>
     <row r="18" ht="13.199999999999999">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
     </row>
     <row r="19" ht="13.199999999999999">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
     </row>
     <row r="20" ht="13.199999999999999">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
     </row>
     <row r="21" ht="13.199999999999999">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
     </row>
     <row r="22" ht="13.199999999999999">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
     </row>
     <row r="23" ht="13.199999999999999">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
     </row>
     <row r="24" ht="13.199999999999999">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
     </row>
     <row r="25" ht="13.199999999999999">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
     </row>
     <row r="26" ht="13.199999999999999">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
     </row>
     <row r="27" ht="13.199999999999999">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
     </row>
     <row r="28" ht="13.199999999999999">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
     </row>
     <row r="29" ht="13.199999999999999">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
     </row>
     <row r="30" ht="13.199999999999999">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
     </row>
     <row r="31" ht="13.199999999999999">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
     </row>
     <row r="32" ht="13.199999999999999">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
     </row>
     <row r="33" ht="13.199999999999999">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
     </row>
     <row r="34" ht="13.199999999999999">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
     </row>
     <row r="35" ht="13.199999999999999">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
     </row>
     <row r="36" ht="13.199999999999999">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
     </row>
     <row r="37" ht="13.199999999999999">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
     </row>
     <row r="38" ht="13.199999999999999">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
     </row>
     <row r="39" ht="13.199999999999999">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
     </row>
     <row r="40" ht="13.199999999999999">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
     </row>
     <row r="41" ht="13.199999999999999">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
     </row>
     <row r="42" ht="13.199999999999999">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
     </row>
     <row r="43" ht="13.199999999999999">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
     </row>
     <row r="44" ht="13.199999999999999">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -3073,17 +3127,17 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00CC00E6-0093-4AED-AB04-00AC000200BE}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00D300BE-00D9-4AF6-99A1-009F000800B6}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1- Not Started, 2- In Progress, 3- Completed"</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H44</xm:sqref>
+          <xm:sqref>H2:H12 H15 H16:H44 H13 H14</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{009300A9-00B4-4496-8BD6-003700D4006A}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{007200A6-001E-464A-BA1B-00FE005800F6}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"MUST HAVE, SHOULD HAVE, COULD HAVE, WON'T HAVE"</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E44</xm:sqref>
+          <xm:sqref>E2:E12 E15 E16:E44 E13 E14</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3099,1922 +3153,1922 @@
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.1093799999999998" defaultRowHeight="10.199999999999999" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="11" width="10"/>
-    <col customWidth="1" min="2" max="2" style="12" width="9.6640599999999992"/>
-    <col customWidth="1" min="3" max="3" style="13" width="41.332000000000001"/>
-    <col customWidth="1" min="4" max="4" style="14" width="11.4414"/>
-    <col customWidth="1" min="5" max="5" style="15" width="11.4414"/>
-    <col customWidth="1" min="6" max="6" style="16" width="9.6640599999999992"/>
-    <col customWidth="1" min="7" max="7" style="11" width="17"/>
-    <col customWidth="1" min="8" max="8" style="11" width="13.332000000000001"/>
-    <col customWidth="1" min="9" max="9" style="11" width="9.3320299999999996"/>
-    <col customWidth="1" min="10" max="10" style="11" width="10.886699999999999"/>
-    <col customWidth="1" min="11" max="11" style="11" width="10.332000000000001"/>
-    <col customWidth="1" min="12" max="12" style="11" width="10.109400000000001"/>
-    <col customWidth="1" min="13" max="257" style="11" width="9.1093799999999998"/>
+    <col customWidth="1" min="1" max="1" style="13" width="10"/>
+    <col customWidth="1" min="2" max="2" style="14" width="9.6640599999999992"/>
+    <col customWidth="1" min="3" max="3" style="15" width="41.332000000000001"/>
+    <col customWidth="1" min="4" max="4" style="16" width="11.4414"/>
+    <col customWidth="1" min="5" max="5" style="17" width="11.4414"/>
+    <col customWidth="1" min="6" max="6" style="18" width="9.6640599999999992"/>
+    <col customWidth="1" min="7" max="7" style="13" width="17"/>
+    <col customWidth="1" min="8" max="8" style="13" width="13.332000000000001"/>
+    <col customWidth="1" min="9" max="9" style="13" width="9.3320299999999996"/>
+    <col customWidth="1" min="10" max="10" style="13" width="10.886699999999999"/>
+    <col customWidth="1" min="11" max="11" style="13" width="10.332000000000001"/>
+    <col customWidth="1" min="12" max="12" style="13" width="10.109400000000001"/>
+    <col customWidth="1" min="13" max="257" style="13" width="9.1093799999999998"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="19"/>
-    </row>
-    <row r="2" s="20" customFormat="1" ht="45.75" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="21"/>
+    </row>
+    <row r="2" s="22" customFormat="1" ht="45.75" customHeight="1">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="C2" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="K2" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="L2" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="M2" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="N2" s="26" t="s">
+      <c r="I2" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="O2" s="26" t="s">
+      <c r="J2" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="P2" s="26" t="s">
+      <c r="K2" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="Q2" s="26" t="s">
+      <c r="L2" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="R2" s="26" t="s">
+      <c r="M2" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="S2" s="26" t="s">
+      <c r="N2" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="T2" s="26" t="s">
+      <c r="O2" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="U2" s="26" t="s">
+      <c r="P2" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="V2" s="26" t="s">
+      <c r="Q2" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="R2" s="28" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="3" s="20" customFormat="1" ht="30" customHeight="1">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="31">
+      <c r="S2" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="T2" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="U2" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="V2" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="W2" s="28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" s="22" customFormat="1" ht="30" customHeight="1">
+      <c r="A3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="33">
         <f t="shared" ref="I3:W3" si="0">SUM(I5:I802)</f>
         <v>2.5</v>
       </c>
-      <c r="J3" s="31">
+      <c r="J3" s="33">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="K3" s="31">
+      <c r="K3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L3" s="31">
+      <c r="L3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M3" s="31">
+      <c r="M3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N3" s="31">
+      <c r="N3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O3" s="31">
+      <c r="O3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P3" s="31">
+      <c r="P3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q3" s="31">
+      <c r="Q3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R3" s="31">
+      <c r="R3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S3" s="31">
+      <c r="S3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T3" s="31">
+      <c r="T3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U3" s="31">
+      <c r="U3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V3" s="31">
+      <c r="V3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W3" s="31">
+      <c r="W3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" s="20" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A4" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="32"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="32"/>
-      <c r="T4" s="32"/>
-      <c r="U4" s="32"/>
-      <c r="V4" s="32"/>
-      <c r="W4" s="32"/>
+    <row r="4" s="22" customFormat="1" ht="33.75" customHeight="1">
+      <c r="A4" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
     </row>
     <row r="5" ht="24.75" customHeight="1">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="37" t="s">
+      <c r="B5" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="39" t="s">
+      <c r="G5" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="42">
         <v>2</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="42">
         <v>2</v>
       </c>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="41"/>
-      <c r="S5" s="41"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="40"/>
-      <c r="V5" s="40"/>
-      <c r="W5" s="40"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="42"/>
+      <c r="U5" s="42"/>
+      <c r="V5" s="42"/>
+      <c r="W5" s="42"/>
     </row>
     <row r="6" ht="24.75" customHeight="1">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37" t="s">
+      <c r="B6" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="39" t="s">
+      <c r="G6" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="40">
+      <c r="I6" s="42">
         <v>0.5</v>
       </c>
-      <c r="J6" s="40">
+      <c r="J6" s="42">
         <v>0.5</v>
       </c>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="41"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="41"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
     </row>
     <row r="7" ht="28.5" customHeight="1">
-      <c r="A7" s="42"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="41"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="41"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="43"/>
+      <c r="W7" s="43"/>
     </row>
     <row r="8" ht="36.75" customHeight="1">
-      <c r="A8" s="42"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="41"/>
-      <c r="S8" s="41"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="41"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
     </row>
     <row r="9" ht="33" customHeight="1">
-      <c r="A9" s="42"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="41"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="43"/>
     </row>
     <row r="10" ht="33" customHeight="1">
-      <c r="A10" s="42"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="41"/>
-      <c r="S10" s="41"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="41"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
     </row>
     <row r="11" ht="28.5" customHeight="1">
-      <c r="A11" s="42"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="41"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="41"/>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="41"/>
-      <c r="R11" s="41"/>
-      <c r="S11" s="41"/>
-      <c r="T11" s="41"/>
-      <c r="U11" s="41"/>
-      <c r="V11" s="41"/>
-      <c r="W11" s="41"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="43"/>
+      <c r="W11" s="43"/>
     </row>
     <row r="12" ht="29.25" customHeight="1">
-      <c r="A12" s="42"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="41"/>
-      <c r="S12" s="41"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="41"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="42"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="41"/>
-      <c r="S13" s="41"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="41"/>
-      <c r="V13" s="41"/>
-      <c r="W13" s="41"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="43"/>
+      <c r="W13" s="43"/>
     </row>
     <row r="14" ht="29.25" customHeight="1">
-      <c r="A14" s="42"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="41"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="41"/>
-      <c r="V14" s="41"/>
-      <c r="W14" s="41"/>
+      <c r="A14" s="44"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
+      <c r="V14" s="43"/>
+      <c r="W14" s="43"/>
     </row>
     <row r="15" ht="34.5" customHeight="1">
-      <c r="A15" s="42"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="41"/>
-      <c r="S15" s="41"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-      <c r="V15" s="41"/>
-      <c r="W15" s="41"/>
+      <c r="A15" s="44"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="43"/>
+      <c r="W15" s="43"/>
     </row>
     <row r="16" ht="36.75" customHeight="1">
-      <c r="A16" s="42"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-      <c r="V16" s="41"/>
-      <c r="W16" s="41"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="43"/>
+      <c r="W16" s="43"/>
     </row>
     <row r="17" ht="34.5" customHeight="1">
-      <c r="A17" s="42"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="41"/>
-      <c r="S17" s="41"/>
-      <c r="T17" s="41"/>
-      <c r="U17" s="41"/>
-      <c r="V17" s="41"/>
-      <c r="W17" s="41"/>
+      <c r="A17" s="44"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="43"/>
+      <c r="W17" s="43"/>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="42"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="41"/>
-      <c r="S18" s="41"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="41"/>
-      <c r="V18" s="41"/>
-      <c r="W18" s="41"/>
+      <c r="A18" s="44"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="43"/>
+      <c r="R18" s="43"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="43"/>
+      <c r="U18" s="43"/>
+      <c r="V18" s="43"/>
+      <c r="W18" s="43"/>
     </row>
     <row r="19" ht="39.75" customHeight="1">
-      <c r="A19" s="42"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="41"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="41"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="41"/>
-      <c r="V19" s="41"/>
-      <c r="W19" s="41"/>
+      <c r="A19" s="44"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="43"/>
+      <c r="U19" s="43"/>
+      <c r="V19" s="43"/>
+      <c r="W19" s="43"/>
     </row>
     <row r="20" ht="26.25" customHeight="1">
-      <c r="A20" s="42"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="41"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="41"/>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="41"/>
-      <c r="S20" s="41"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="41"/>
-      <c r="V20" s="41"/>
-      <c r="W20" s="41"/>
+      <c r="A20" s="44"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="43"/>
+      <c r="U20" s="43"/>
+      <c r="V20" s="43"/>
+      <c r="W20" s="43"/>
     </row>
     <row r="21" ht="23.25" customHeight="1">
-      <c r="A21" s="42"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="41"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="41"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="41"/>
-      <c r="S21" s="41"/>
-      <c r="T21" s="41"/>
-      <c r="U21" s="41"/>
-      <c r="V21" s="41"/>
-      <c r="W21" s="41"/>
+      <c r="A21" s="44"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="43"/>
+      <c r="U21" s="43"/>
+      <c r="V21" s="43"/>
+      <c r="W21" s="43"/>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="42"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="41"/>
-      <c r="N22" s="41"/>
-      <c r="O22" s="41"/>
-      <c r="P22" s="41"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="41"/>
-      <c r="S22" s="41"/>
-      <c r="T22" s="41"/>
-      <c r="U22" s="41"/>
-      <c r="V22" s="41"/>
-      <c r="W22" s="41"/>
+      <c r="A22" s="44"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="43"/>
+      <c r="R22" s="43"/>
+      <c r="S22" s="43"/>
+      <c r="T22" s="43"/>
+      <c r="U22" s="43"/>
+      <c r="V22" s="43"/>
+      <c r="W22" s="43"/>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="42"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="40"/>
-      <c r="M23" s="41"/>
-      <c r="N23" s="41"/>
-      <c r="O23" s="41"/>
-      <c r="P23" s="41"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="41"/>
-      <c r="S23" s="41"/>
-      <c r="T23" s="41"/>
-      <c r="U23" s="41"/>
-      <c r="V23" s="41"/>
-      <c r="W23" s="41"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="43"/>
+      <c r="U23" s="43"/>
+      <c r="V23" s="43"/>
+      <c r="W23" s="43"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="42"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="41"/>
-      <c r="N24" s="41"/>
-      <c r="O24" s="41"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="41"/>
-      <c r="R24" s="41"/>
-      <c r="S24" s="41"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="41"/>
-      <c r="V24" s="41"/>
-      <c r="W24" s="41"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="43"/>
+      <c r="T24" s="43"/>
+      <c r="U24" s="43"/>
+      <c r="V24" s="43"/>
+      <c r="W24" s="43"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="42"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="41"/>
-      <c r="S25" s="41"/>
-      <c r="T25" s="41"/>
-      <c r="U25" s="41"/>
-      <c r="V25" s="41"/>
-      <c r="W25" s="41"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="43"/>
+      <c r="U25" s="43"/>
+      <c r="V25" s="43"/>
+      <c r="W25" s="43"/>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="42"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="41"/>
-      <c r="S26" s="41"/>
-      <c r="T26" s="41"/>
-      <c r="U26" s="41"/>
-      <c r="V26" s="41"/>
-      <c r="W26" s="41"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="42"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="41"/>
-      <c r="R27" s="41"/>
-      <c r="S27" s="41"/>
-      <c r="T27" s="41"/>
-      <c r="U27" s="41"/>
-      <c r="V27" s="41"/>
-      <c r="W27" s="41"/>
+      <c r="A27" s="44"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="43"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="43"/>
+      <c r="T27" s="43"/>
+      <c r="U27" s="43"/>
+      <c r="V27" s="43"/>
+      <c r="W27" s="43"/>
     </row>
     <row r="28" ht="29.25" customHeight="1">
-      <c r="A28" s="42"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="41"/>
-      <c r="S28" s="41"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="41"/>
-      <c r="V28" s="41"/>
-      <c r="W28" s="41"/>
+      <c r="A28" s="44"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="43"/>
+      <c r="W28" s="43"/>
     </row>
     <row r="29" ht="20.25" customHeight="1">
-      <c r="A29" s="42"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="41"/>
-      <c r="S29" s="41"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="41"/>
-      <c r="V29" s="41"/>
-      <c r="W29" s="41"/>
+      <c r="A29" s="44"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="43"/>
+      <c r="M29" s="43"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="43"/>
+      <c r="R29" s="43"/>
+      <c r="S29" s="43"/>
+      <c r="T29" s="43"/>
+      <c r="U29" s="43"/>
+      <c r="V29" s="43"/>
+      <c r="W29" s="43"/>
     </row>
     <row r="30" ht="20.25" customHeight="1">
-      <c r="A30" s="42"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="41"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="41"/>
-      <c r="S30" s="41"/>
-      <c r="T30" s="41"/>
-      <c r="U30" s="41"/>
-      <c r="V30" s="41"/>
-      <c r="W30" s="41"/>
+      <c r="A30" s="44"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="43"/>
+      <c r="V30" s="43"/>
+      <c r="W30" s="43"/>
     </row>
     <row r="31" ht="20.25" customHeight="1">
-      <c r="A31" s="42"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
-      <c r="N31" s="41"/>
-      <c r="O31" s="41"/>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="41"/>
-      <c r="S31" s="41"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="41"/>
-      <c r="V31" s="41"/>
-      <c r="W31" s="41"/>
+      <c r="A31" s="44"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="43"/>
+      <c r="R31" s="43"/>
+      <c r="S31" s="43"/>
+      <c r="T31" s="43"/>
+      <c r="U31" s="43"/>
+      <c r="V31" s="43"/>
+      <c r="W31" s="43"/>
     </row>
     <row r="32" ht="20.25" customHeight="1">
-      <c r="A32" s="42"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="41"/>
-      <c r="L32" s="41"/>
-      <c r="M32" s="41"/>
-      <c r="N32" s="41"/>
-      <c r="O32" s="41"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="41"/>
-      <c r="S32" s="41"/>
-      <c r="T32" s="41"/>
-      <c r="U32" s="41"/>
-      <c r="V32" s="41"/>
-      <c r="W32" s="41"/>
+      <c r="A32" s="44"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="43"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="43"/>
+      <c r="Q32" s="43"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="43"/>
+      <c r="T32" s="43"/>
+      <c r="U32" s="43"/>
+      <c r="V32" s="43"/>
+      <c r="W32" s="43"/>
     </row>
     <row r="33" ht="20.25" customHeight="1">
-      <c r="A33" s="42"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="41"/>
-      <c r="O33" s="41"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="41"/>
-      <c r="S33" s="41"/>
-      <c r="T33" s="41"/>
-      <c r="U33" s="41"/>
-      <c r="V33" s="41"/>
-      <c r="W33" s="41"/>
+      <c r="A33" s="44"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="43"/>
+      <c r="M33" s="43"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="43"/>
+      <c r="Q33" s="43"/>
+      <c r="R33" s="43"/>
+      <c r="S33" s="43"/>
+      <c r="T33" s="43"/>
+      <c r="U33" s="43"/>
+      <c r="V33" s="43"/>
+      <c r="W33" s="43"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="42"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="41"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="41"/>
-      <c r="S34" s="41"/>
-      <c r="T34" s="41"/>
-      <c r="U34" s="41"/>
-      <c r="V34" s="41"/>
-      <c r="W34" s="41"/>
+      <c r="A34" s="44"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="43"/>
+      <c r="Q34" s="43"/>
+      <c r="R34" s="43"/>
+      <c r="S34" s="43"/>
+      <c r="T34" s="43"/>
+      <c r="U34" s="43"/>
+      <c r="V34" s="43"/>
+      <c r="W34" s="43"/>
     </row>
     <row r="35" ht="21" customHeight="1">
-      <c r="A35" s="42"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
-      <c r="M35" s="41"/>
-      <c r="N35" s="41"/>
-      <c r="O35" s="41"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="41"/>
-      <c r="S35" s="41"/>
-      <c r="T35" s="41"/>
-      <c r="U35" s="41"/>
-      <c r="V35" s="41"/>
-      <c r="W35" s="41"/>
+      <c r="A35" s="44"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="43"/>
+      <c r="Q35" s="43"/>
+      <c r="R35" s="43"/>
+      <c r="S35" s="43"/>
+      <c r="T35" s="43"/>
+      <c r="U35" s="43"/>
+      <c r="V35" s="43"/>
+      <c r="W35" s="43"/>
     </row>
     <row r="36" ht="21.75" customHeight="1">
-      <c r="A36" s="42"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="41"/>
-      <c r="M36" s="41"/>
-      <c r="N36" s="41"/>
-      <c r="O36" s="41"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="41"/>
-      <c r="S36" s="41"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
-      <c r="V36" s="41"/>
-      <c r="W36" s="41"/>
+      <c r="A36" s="44"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="43"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="43"/>
+      <c r="T36" s="43"/>
+      <c r="U36" s="43"/>
+      <c r="V36" s="43"/>
+      <c r="W36" s="43"/>
     </row>
     <row r="37" ht="21.75" customHeight="1">
-      <c r="A37" s="42"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="41"/>
-      <c r="K37" s="41"/>
-      <c r="L37" s="41"/>
-      <c r="M37" s="41"/>
-      <c r="N37" s="41"/>
-      <c r="O37" s="41"/>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="41"/>
-      <c r="S37" s="41"/>
-      <c r="T37" s="41"/>
-      <c r="U37" s="41"/>
-      <c r="V37" s="41"/>
-      <c r="W37" s="41"/>
+      <c r="A37" s="44"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="43"/>
+      <c r="Q37" s="43"/>
+      <c r="R37" s="43"/>
+      <c r="S37" s="43"/>
+      <c r="T37" s="43"/>
+      <c r="U37" s="43"/>
+      <c r="V37" s="43"/>
+      <c r="W37" s="43"/>
     </row>
     <row r="38" ht="21.75" customHeight="1">
-      <c r="A38" s="42"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="41"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="41"/>
-      <c r="N38" s="41"/>
-      <c r="O38" s="41"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="41"/>
-      <c r="S38" s="41"/>
-      <c r="T38" s="41"/>
-      <c r="U38" s="41"/>
-      <c r="V38" s="41"/>
-      <c r="W38" s="41"/>
+      <c r="A38" s="44"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="43"/>
+      <c r="N38" s="43"/>
+      <c r="O38" s="43"/>
+      <c r="P38" s="43"/>
+      <c r="Q38" s="43"/>
+      <c r="R38" s="43"/>
+      <c r="S38" s="43"/>
+      <c r="T38" s="43"/>
+      <c r="U38" s="43"/>
+      <c r="V38" s="43"/>
+      <c r="W38" s="43"/>
     </row>
     <row r="39" ht="21.75" customHeight="1">
-      <c r="A39" s="42"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="41"/>
-      <c r="M39" s="41"/>
-      <c r="N39" s="41"/>
-      <c r="O39" s="41"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="41"/>
-      <c r="S39" s="41"/>
-      <c r="T39" s="41"/>
-      <c r="U39" s="41"/>
-      <c r="V39" s="41"/>
-      <c r="W39" s="41"/>
+      <c r="A39" s="44"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="43"/>
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="43"/>
+      <c r="T39" s="43"/>
+      <c r="U39" s="43"/>
+      <c r="V39" s="43"/>
+      <c r="W39" s="43"/>
     </row>
     <row r="40" ht="21.75" customHeight="1">
-      <c r="A40" s="42"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="41"/>
-      <c r="K40" s="41"/>
-      <c r="L40" s="41"/>
-      <c r="M40" s="41"/>
-      <c r="N40" s="41"/>
-      <c r="O40" s="41"/>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="41"/>
-      <c r="S40" s="41"/>
-      <c r="T40" s="41"/>
-      <c r="U40" s="41"/>
-      <c r="V40" s="41"/>
-      <c r="W40" s="41"/>
+      <c r="A40" s="44"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="43"/>
+      <c r="N40" s="43"/>
+      <c r="O40" s="43"/>
+      <c r="P40" s="43"/>
+      <c r="Q40" s="43"/>
+      <c r="R40" s="43"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="43"/>
+      <c r="U40" s="43"/>
+      <c r="V40" s="43"/>
+      <c r="W40" s="43"/>
     </row>
     <row r="41" ht="21" customHeight="1">
-      <c r="A41" s="42"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="41"/>
-      <c r="K41" s="41"/>
-      <c r="L41" s="41"/>
-      <c r="M41" s="41"/>
-      <c r="N41" s="41"/>
-      <c r="O41" s="41"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="41"/>
-      <c r="S41" s="41"/>
-      <c r="T41" s="41"/>
-      <c r="U41" s="41"/>
-      <c r="V41" s="41"/>
-      <c r="W41" s="41"/>
+      <c r="A41" s="44"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="43"/>
+      <c r="M41" s="43"/>
+      <c r="N41" s="43"/>
+      <c r="O41" s="43"/>
+      <c r="P41" s="43"/>
+      <c r="Q41" s="43"/>
+      <c r="R41" s="43"/>
+      <c r="S41" s="43"/>
+      <c r="T41" s="43"/>
+      <c r="U41" s="43"/>
+      <c r="V41" s="43"/>
+      <c r="W41" s="43"/>
     </row>
     <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="42"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="40"/>
-      <c r="J42" s="41"/>
-      <c r="K42" s="41"/>
-      <c r="L42" s="41"/>
-      <c r="M42" s="41"/>
-      <c r="N42" s="41"/>
-      <c r="O42" s="41"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="41"/>
-      <c r="S42" s="41"/>
-      <c r="T42" s="41"/>
-      <c r="U42" s="41"/>
-      <c r="V42" s="41"/>
-      <c r="W42" s="41"/>
+      <c r="A42" s="44"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+      <c r="L42" s="43"/>
+      <c r="M42" s="43"/>
+      <c r="N42" s="43"/>
+      <c r="O42" s="43"/>
+      <c r="P42" s="43"/>
+      <c r="Q42" s="43"/>
+      <c r="R42" s="43"/>
+      <c r="S42" s="43"/>
+      <c r="T42" s="43"/>
+      <c r="U42" s="43"/>
+      <c r="V42" s="43"/>
+      <c r="W42" s="43"/>
     </row>
     <row r="43" ht="17.25" customHeight="1">
-      <c r="A43" s="42"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="40"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="41"/>
-      <c r="L43" s="41"/>
-      <c r="M43" s="41"/>
-      <c r="N43" s="41"/>
-      <c r="O43" s="41"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="41"/>
-      <c r="S43" s="41"/>
-      <c r="T43" s="41"/>
-      <c r="U43" s="41"/>
-      <c r="V43" s="41"/>
-      <c r="W43" s="41"/>
+      <c r="A43" s="44"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+      <c r="L43" s="43"/>
+      <c r="M43" s="43"/>
+      <c r="N43" s="43"/>
+      <c r="O43" s="43"/>
+      <c r="P43" s="43"/>
+      <c r="Q43" s="43"/>
+      <c r="R43" s="43"/>
+      <c r="S43" s="43"/>
+      <c r="T43" s="43"/>
+      <c r="U43" s="43"/>
+      <c r="V43" s="43"/>
+      <c r="W43" s="43"/>
     </row>
     <row r="44" ht="17.25" customHeight="1">
-      <c r="A44" s="42"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
-      <c r="L44" s="41"/>
-      <c r="M44" s="41"/>
-      <c r="N44" s="41"/>
-      <c r="O44" s="41"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="41"/>
-      <c r="S44" s="41"/>
-      <c r="T44" s="41"/>
-      <c r="U44" s="41"/>
-      <c r="V44" s="41"/>
-      <c r="W44" s="41"/>
+      <c r="A44" s="44"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+      <c r="L44" s="43"/>
+      <c r="M44" s="43"/>
+      <c r="N44" s="43"/>
+      <c r="O44" s="43"/>
+      <c r="P44" s="43"/>
+      <c r="Q44" s="43"/>
+      <c r="R44" s="43"/>
+      <c r="S44" s="43"/>
+      <c r="T44" s="43"/>
+      <c r="U44" s="43"/>
+      <c r="V44" s="43"/>
+      <c r="W44" s="43"/>
     </row>
     <row r="45" ht="17.25" customHeight="1">
-      <c r="A45" s="42"/>
-      <c r="B45" s="34"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
-      <c r="N45" s="41"/>
-      <c r="O45" s="41"/>
-      <c r="P45" s="41"/>
-      <c r="Q45" s="41"/>
-      <c r="R45" s="41"/>
-      <c r="S45" s="41"/>
-      <c r="T45" s="41"/>
-      <c r="U45" s="41"/>
-      <c r="V45" s="41"/>
-      <c r="W45" s="41"/>
+      <c r="A45" s="44"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="38"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+      <c r="L45" s="43"/>
+      <c r="M45" s="43"/>
+      <c r="N45" s="43"/>
+      <c r="O45" s="43"/>
+      <c r="P45" s="43"/>
+      <c r="Q45" s="43"/>
+      <c r="R45" s="43"/>
+      <c r="S45" s="43"/>
+      <c r="T45" s="43"/>
+      <c r="U45" s="43"/>
+      <c r="V45" s="43"/>
+      <c r="W45" s="43"/>
     </row>
     <row r="46" ht="17.25" customHeight="1">
-      <c r="A46" s="42"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="39"/>
-      <c r="I46" s="40"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="41"/>
-      <c r="M46" s="41"/>
-      <c r="N46" s="41"/>
-      <c r="O46" s="41"/>
-      <c r="P46" s="41"/>
-      <c r="Q46" s="41"/>
-      <c r="R46" s="41"/>
-      <c r="S46" s="41"/>
-      <c r="T46" s="41"/>
-      <c r="U46" s="41"/>
-      <c r="V46" s="41"/>
-      <c r="W46" s="41"/>
+      <c r="A46" s="44"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="39"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="43"/>
+      <c r="M46" s="43"/>
+      <c r="N46" s="43"/>
+      <c r="O46" s="43"/>
+      <c r="P46" s="43"/>
+      <c r="Q46" s="43"/>
+      <c r="R46" s="43"/>
+      <c r="S46" s="43"/>
+      <c r="T46" s="43"/>
+      <c r="U46" s="43"/>
+      <c r="V46" s="43"/>
+      <c r="W46" s="43"/>
     </row>
     <row r="47" ht="17.25" customHeight="1">
-      <c r="A47" s="42"/>
-      <c r="B47" s="34"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="39"/>
-      <c r="I47" s="40"/>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="41"/>
-      <c r="M47" s="41"/>
-      <c r="N47" s="41"/>
-      <c r="O47" s="41"/>
-      <c r="P47" s="41"/>
-      <c r="Q47" s="41"/>
-      <c r="R47" s="41"/>
-      <c r="S47" s="41"/>
-      <c r="T47" s="41"/>
-      <c r="U47" s="41"/>
-      <c r="V47" s="41"/>
-      <c r="W47" s="41"/>
+      <c r="A47" s="44"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+      <c r="L47" s="43"/>
+      <c r="M47" s="43"/>
+      <c r="N47" s="43"/>
+      <c r="O47" s="43"/>
+      <c r="P47" s="43"/>
+      <c r="Q47" s="43"/>
+      <c r="R47" s="43"/>
+      <c r="S47" s="43"/>
+      <c r="T47" s="43"/>
+      <c r="U47" s="43"/>
+      <c r="V47" s="43"/>
+      <c r="W47" s="43"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="42"/>
-      <c r="B48" s="34"/>
-      <c r="C48" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="39"/>
-      <c r="I48" s="40"/>
-      <c r="J48" s="41"/>
-      <c r="K48" s="41"/>
-      <c r="L48" s="41"/>
-      <c r="M48" s="41"/>
-      <c r="N48" s="41"/>
-      <c r="O48" s="41"/>
-      <c r="P48" s="41"/>
-      <c r="Q48" s="41"/>
-      <c r="R48" s="41"/>
-      <c r="S48" s="41"/>
-      <c r="T48" s="41"/>
-      <c r="U48" s="41"/>
-      <c r="V48" s="41"/>
-      <c r="W48" s="41"/>
+      <c r="A48" s="44"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D48" s="38"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+      <c r="L48" s="43"/>
+      <c r="M48" s="43"/>
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="43"/>
+      <c r="T48" s="43"/>
+      <c r="U48" s="43"/>
+      <c r="V48" s="43"/>
+      <c r="W48" s="43"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
-      <c r="A49" s="42"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="39"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
-      <c r="M49" s="41"/>
-      <c r="N49" s="41"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="41"/>
-      <c r="R49" s="41"/>
-      <c r="S49" s="41"/>
-      <c r="T49" s="41"/>
-      <c r="U49" s="41"/>
-      <c r="V49" s="41"/>
-      <c r="W49" s="41"/>
+      <c r="A49" s="44"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" s="38"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+      <c r="L49" s="43"/>
+      <c r="M49" s="43"/>
+      <c r="N49" s="43"/>
+      <c r="O49" s="43"/>
+      <c r="P49" s="43"/>
+      <c r="Q49" s="43"/>
+      <c r="R49" s="43"/>
+      <c r="S49" s="43"/>
+      <c r="T49" s="43"/>
+      <c r="U49" s="43"/>
+      <c r="V49" s="43"/>
+      <c r="W49" s="43"/>
     </row>
     <row r="50" ht="19.5" customHeight="1">
-      <c r="A50" s="42"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D50" s="36"/>
-      <c r="E50" s="36"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="39"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="41"/>
-      <c r="M50" s="41"/>
-      <c r="N50" s="41"/>
-      <c r="O50" s="41"/>
-      <c r="P50" s="41"/>
-      <c r="Q50" s="41"/>
-      <c r="R50" s="41"/>
-      <c r="S50" s="41"/>
-      <c r="T50" s="41"/>
-      <c r="U50" s="41"/>
-      <c r="V50" s="41"/>
-      <c r="W50" s="41"/>
+      <c r="A50" s="44"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+      <c r="L50" s="43"/>
+      <c r="M50" s="43"/>
+      <c r="N50" s="43"/>
+      <c r="O50" s="43"/>
+      <c r="P50" s="43"/>
+      <c r="Q50" s="43"/>
+      <c r="R50" s="43"/>
+      <c r="S50" s="43"/>
+      <c r="T50" s="43"/>
+      <c r="U50" s="43"/>
+      <c r="V50" s="43"/>
+      <c r="W50" s="43"/>
     </row>
     <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="42"/>
-      <c r="B51" s="34"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="36"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="39"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="41"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="41"/>
-      <c r="M51" s="41"/>
-      <c r="N51" s="41"/>
-      <c r="O51" s="41"/>
-      <c r="P51" s="41"/>
-      <c r="Q51" s="41"/>
-      <c r="R51" s="41"/>
-      <c r="S51" s="41"/>
-      <c r="T51" s="41"/>
-      <c r="U51" s="41"/>
-      <c r="V51" s="41"/>
-      <c r="W51" s="41"/>
+      <c r="A51" s="44"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+      <c r="L51" s="43"/>
+      <c r="M51" s="43"/>
+      <c r="N51" s="43"/>
+      <c r="O51" s="43"/>
+      <c r="P51" s="43"/>
+      <c r="Q51" s="43"/>
+      <c r="R51" s="43"/>
+      <c r="S51" s="43"/>
+      <c r="T51" s="43"/>
+      <c r="U51" s="43"/>
+      <c r="V51" s="43"/>
+      <c r="W51" s="43"/>
     </row>
     <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="42"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="43"/>
-      <c r="D52" s="36"/>
-      <c r="E52" s="36"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="40"/>
-      <c r="J52" s="41"/>
-      <c r="K52" s="41"/>
-      <c r="L52" s="41"/>
-      <c r="M52" s="41"/>
-      <c r="N52" s="41"/>
-      <c r="O52" s="41"/>
-      <c r="P52" s="41"/>
-      <c r="Q52" s="41"/>
-      <c r="R52" s="41"/>
-      <c r="S52" s="41"/>
-      <c r="T52" s="41"/>
-      <c r="U52" s="41"/>
-      <c r="V52" s="41"/>
-      <c r="W52" s="41"/>
+      <c r="A52" s="44"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="43"/>
+      <c r="L52" s="43"/>
+      <c r="M52" s="43"/>
+      <c r="N52" s="43"/>
+      <c r="O52" s="43"/>
+      <c r="P52" s="43"/>
+      <c r="Q52" s="43"/>
+      <c r="R52" s="43"/>
+      <c r="S52" s="43"/>
+      <c r="T52" s="43"/>
+      <c r="U52" s="43"/>
+      <c r="V52" s="43"/>
+      <c r="W52" s="43"/>
     </row>
     <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="42"/>
-      <c r="B53" s="34"/>
-      <c r="C53" s="43"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="37"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="41"/>
-      <c r="K53" s="41"/>
-      <c r="L53" s="41"/>
-      <c r="M53" s="41"/>
-      <c r="N53" s="41"/>
-      <c r="O53" s="41"/>
-      <c r="P53" s="41"/>
-      <c r="Q53" s="41"/>
-      <c r="R53" s="41"/>
-      <c r="S53" s="41"/>
-      <c r="T53" s="41"/>
-      <c r="U53" s="41"/>
-      <c r="V53" s="41"/>
-      <c r="W53" s="41"/>
+      <c r="A53" s="44"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+      <c r="L53" s="43"/>
+      <c r="M53" s="43"/>
+      <c r="N53" s="43"/>
+      <c r="O53" s="43"/>
+      <c r="P53" s="43"/>
+      <c r="Q53" s="43"/>
+      <c r="R53" s="43"/>
+      <c r="S53" s="43"/>
+      <c r="T53" s="43"/>
+      <c r="U53" s="43"/>
+      <c r="V53" s="43"/>
+      <c r="W53" s="43"/>
     </row>
     <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="42"/>
-      <c r="B54" s="34"/>
-      <c r="C54" s="43"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="37"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="40"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="41"/>
-      <c r="M54" s="41"/>
-      <c r="N54" s="41"/>
-      <c r="O54" s="41"/>
-      <c r="P54" s="41"/>
-      <c r="Q54" s="41"/>
-      <c r="R54" s="41"/>
-      <c r="S54" s="41"/>
-      <c r="T54" s="41"/>
-      <c r="U54" s="41"/>
-      <c r="V54" s="41"/>
-      <c r="W54" s="41"/>
+      <c r="A54" s="44"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="45"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43"/>
+      <c r="L54" s="43"/>
+      <c r="M54" s="43"/>
+      <c r="N54" s="43"/>
+      <c r="O54" s="43"/>
+      <c r="P54" s="43"/>
+      <c r="Q54" s="43"/>
+      <c r="R54" s="43"/>
+      <c r="S54" s="43"/>
+      <c r="T54" s="43"/>
+      <c r="U54" s="43"/>
+      <c r="V54" s="43"/>
+      <c r="W54" s="43"/>
     </row>
     <row r="55" ht="20.25" customHeight="1">
-      <c r="A55" s="42"/>
-      <c r="B55" s="34"/>
-      <c r="C55" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="41"/>
-      <c r="K55" s="41"/>
-      <c r="L55" s="41"/>
-      <c r="M55" s="41"/>
-      <c r="N55" s="41"/>
-      <c r="O55" s="41"/>
-      <c r="P55" s="41"/>
-      <c r="Q55" s="41"/>
-      <c r="R55" s="41"/>
-      <c r="S55" s="41"/>
-      <c r="T55" s="41"/>
-      <c r="U55" s="41"/>
-      <c r="V55" s="41"/>
-      <c r="W55" s="41"/>
+      <c r="A55" s="44"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="38"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="39"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="42"/>
+      <c r="J55" s="43"/>
+      <c r="K55" s="43"/>
+      <c r="L55" s="43"/>
+      <c r="M55" s="43"/>
+      <c r="N55" s="43"/>
+      <c r="O55" s="43"/>
+      <c r="P55" s="43"/>
+      <c r="Q55" s="43"/>
+      <c r="R55" s="43"/>
+      <c r="S55" s="43"/>
+      <c r="T55" s="43"/>
+      <c r="U55" s="43"/>
+      <c r="V55" s="43"/>
+      <c r="W55" s="43"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="42"/>
-      <c r="B56" s="34"/>
-      <c r="C56" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="40"/>
-      <c r="J56" s="41"/>
-      <c r="K56" s="41"/>
-      <c r="L56" s="41"/>
-      <c r="M56" s="41"/>
-      <c r="N56" s="41"/>
-      <c r="O56" s="41"/>
-      <c r="P56" s="41"/>
-      <c r="Q56" s="41"/>
-      <c r="R56" s="41"/>
-      <c r="S56" s="41"/>
-      <c r="T56" s="41"/>
-      <c r="U56" s="41"/>
-      <c r="V56" s="41"/>
-      <c r="W56" s="41"/>
+      <c r="A56" s="44"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D56" s="38"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="39"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="42"/>
+      <c r="J56" s="43"/>
+      <c r="K56" s="43"/>
+      <c r="L56" s="43"/>
+      <c r="M56" s="43"/>
+      <c r="N56" s="43"/>
+      <c r="O56" s="43"/>
+      <c r="P56" s="43"/>
+      <c r="Q56" s="43"/>
+      <c r="R56" s="43"/>
+      <c r="S56" s="43"/>
+      <c r="T56" s="43"/>
+      <c r="U56" s="43"/>
+      <c r="V56" s="43"/>
+      <c r="W56" s="43"/>
     </row>
     <row r="57" ht="17.25" customHeight="1">
-      <c r="A57" s="42"/>
-      <c r="B57" s="34"/>
-      <c r="C57" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D57" s="36"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="39"/>
-      <c r="I57" s="40"/>
-      <c r="J57" s="41"/>
-      <c r="K57" s="41"/>
-      <c r="L57" s="41"/>
-      <c r="M57" s="41"/>
-      <c r="N57" s="41"/>
-      <c r="O57" s="41"/>
-      <c r="P57" s="41"/>
-      <c r="Q57" s="41"/>
-      <c r="R57" s="41"/>
-      <c r="S57" s="41"/>
-      <c r="T57" s="41"/>
-      <c r="U57" s="41"/>
-      <c r="V57" s="41"/>
-      <c r="W57" s="41"/>
+      <c r="A57" s="44"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" s="38"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="39"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="42"/>
+      <c r="J57" s="43"/>
+      <c r="K57" s="43"/>
+      <c r="L57" s="43"/>
+      <c r="M57" s="43"/>
+      <c r="N57" s="43"/>
+      <c r="O57" s="43"/>
+      <c r="P57" s="43"/>
+      <c r="Q57" s="43"/>
+      <c r="R57" s="43"/>
+      <c r="S57" s="43"/>
+      <c r="T57" s="43"/>
+      <c r="U57" s="43"/>
+      <c r="V57" s="43"/>
+      <c r="W57" s="43"/>
     </row>
     <row r="58" ht="17.25" customHeight="1">
-      <c r="A58" s="42"/>
-      <c r="B58" s="34"/>
-      <c r="C58" s="43"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="39"/>
-      <c r="I58" s="40"/>
-      <c r="J58" s="41"/>
-      <c r="K58" s="41"/>
-      <c r="L58" s="41"/>
-      <c r="M58" s="41"/>
-      <c r="N58" s="41"/>
-      <c r="O58" s="41"/>
-      <c r="P58" s="41"/>
-      <c r="Q58" s="41"/>
-      <c r="R58" s="41"/>
-      <c r="S58" s="41"/>
-      <c r="T58" s="41"/>
-      <c r="U58" s="41"/>
-      <c r="V58" s="41"/>
-      <c r="W58" s="41"/>
+      <c r="A58" s="44"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="45"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="39"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="41"/>
+      <c r="I58" s="42"/>
+      <c r="J58" s="43"/>
+      <c r="K58" s="43"/>
+      <c r="L58" s="43"/>
+      <c r="M58" s="43"/>
+      <c r="N58" s="43"/>
+      <c r="O58" s="43"/>
+      <c r="P58" s="43"/>
+      <c r="Q58" s="43"/>
+      <c r="R58" s="43"/>
+      <c r="S58" s="43"/>
+      <c r="T58" s="43"/>
+      <c r="U58" s="43"/>
+      <c r="V58" s="43"/>
+      <c r="W58" s="43"/>
     </row>
     <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="42"/>
-      <c r="B59" s="34"/>
-      <c r="C59" s="43"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="36"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="40"/>
-      <c r="J59" s="41"/>
-      <c r="K59" s="41"/>
-      <c r="L59" s="41"/>
-      <c r="M59" s="41"/>
-      <c r="N59" s="41"/>
-      <c r="O59" s="41"/>
-      <c r="P59" s="41"/>
-      <c r="Q59" s="41"/>
-      <c r="R59" s="41"/>
-      <c r="S59" s="41"/>
-      <c r="T59" s="41"/>
-      <c r="U59" s="41"/>
-      <c r="V59" s="41"/>
-      <c r="W59" s="41"/>
+      <c r="A59" s="44"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="45"/>
+      <c r="D59" s="38"/>
+      <c r="E59" s="38"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="42"/>
+      <c r="J59" s="43"/>
+      <c r="K59" s="43"/>
+      <c r="L59" s="43"/>
+      <c r="M59" s="43"/>
+      <c r="N59" s="43"/>
+      <c r="O59" s="43"/>
+      <c r="P59" s="43"/>
+      <c r="Q59" s="43"/>
+      <c r="R59" s="43"/>
+      <c r="S59" s="43"/>
+      <c r="T59" s="43"/>
+      <c r="U59" s="43"/>
+      <c r="V59" s="43"/>
+      <c r="W59" s="43"/>
     </row>
     <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="42"/>
-      <c r="B60" s="34"/>
-      <c r="C60" s="43"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="39"/>
-      <c r="I60" s="40"/>
-      <c r="J60" s="41"/>
-      <c r="K60" s="41"/>
-      <c r="L60" s="41"/>
-      <c r="M60" s="41"/>
-      <c r="N60" s="41"/>
-      <c r="O60" s="41"/>
-      <c r="P60" s="41"/>
-      <c r="Q60" s="41"/>
-      <c r="R60" s="41"/>
-      <c r="S60" s="41"/>
-      <c r="T60" s="41"/>
-      <c r="U60" s="41"/>
-      <c r="V60" s="41"/>
-      <c r="W60" s="41"/>
+      <c r="A60" s="44"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="45"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="38"/>
+      <c r="F60" s="39"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="41"/>
+      <c r="I60" s="42"/>
+      <c r="J60" s="43"/>
+      <c r="K60" s="43"/>
+      <c r="L60" s="43"/>
+      <c r="M60" s="43"/>
+      <c r="N60" s="43"/>
+      <c r="O60" s="43"/>
+      <c r="P60" s="43"/>
+      <c r="Q60" s="43"/>
+      <c r="R60" s="43"/>
+      <c r="S60" s="43"/>
+      <c r="T60" s="43"/>
+      <c r="U60" s="43"/>
+      <c r="V60" s="43"/>
+      <c r="W60" s="43"/>
     </row>
     <row r="61" ht="17.25" customHeight="1">
-      <c r="A61" s="42"/>
-      <c r="B61" s="34"/>
-      <c r="C61" s="43"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="39"/>
-      <c r="I61" s="40"/>
-      <c r="J61" s="41"/>
-      <c r="K61" s="41"/>
-      <c r="L61" s="41"/>
-      <c r="M61" s="41"/>
-      <c r="N61" s="41"/>
-      <c r="O61" s="41"/>
-      <c r="P61" s="41"/>
-      <c r="Q61" s="41"/>
-      <c r="R61" s="41"/>
-      <c r="S61" s="41"/>
-      <c r="T61" s="41"/>
-      <c r="U61" s="41"/>
-      <c r="V61" s="41"/>
-      <c r="W61" s="41"/>
+      <c r="A61" s="44"/>
+      <c r="B61" s="36"/>
+      <c r="C61" s="45"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="40"/>
+      <c r="H61" s="41"/>
+      <c r="I61" s="42"/>
+      <c r="J61" s="43"/>
+      <c r="K61" s="43"/>
+      <c r="L61" s="43"/>
+      <c r="M61" s="43"/>
+      <c r="N61" s="43"/>
+      <c r="O61" s="43"/>
+      <c r="P61" s="43"/>
+      <c r="Q61" s="43"/>
+      <c r="R61" s="43"/>
+      <c r="S61" s="43"/>
+      <c r="T61" s="43"/>
+      <c r="U61" s="43"/>
+      <c r="V61" s="43"/>
+      <c r="W61" s="43"/>
     </row>
     <row r="62" ht="18.75" customHeight="1">
-      <c r="A62" s="42"/>
-      <c r="B62" s="34"/>
-      <c r="C62" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D62" s="36"/>
-      <c r="E62" s="36"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="39"/>
-      <c r="I62" s="40"/>
-      <c r="J62" s="41"/>
-      <c r="K62" s="41"/>
-      <c r="L62" s="41"/>
-      <c r="M62" s="41"/>
-      <c r="N62" s="41"/>
-      <c r="O62" s="41"/>
-      <c r="P62" s="41"/>
-      <c r="Q62" s="41"/>
-      <c r="R62" s="41"/>
-      <c r="S62" s="41"/>
-      <c r="T62" s="41"/>
-      <c r="U62" s="41"/>
-      <c r="V62" s="41"/>
-      <c r="W62" s="41"/>
+      <c r="A62" s="44"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D62" s="38"/>
+      <c r="E62" s="38"/>
+      <c r="F62" s="39"/>
+      <c r="G62" s="40"/>
+      <c r="H62" s="41"/>
+      <c r="I62" s="42"/>
+      <c r="J62" s="43"/>
+      <c r="K62" s="43"/>
+      <c r="L62" s="43"/>
+      <c r="M62" s="43"/>
+      <c r="N62" s="43"/>
+      <c r="O62" s="43"/>
+      <c r="P62" s="43"/>
+      <c r="Q62" s="43"/>
+      <c r="R62" s="43"/>
+      <c r="S62" s="43"/>
+      <c r="T62" s="43"/>
+      <c r="U62" s="43"/>
+      <c r="V62" s="43"/>
+      <c r="W62" s="43"/>
     </row>
     <row r="63" ht="18.75" customHeight="1">
-      <c r="A63" s="42"/>
-      <c r="B63" s="34"/>
-      <c r="C63" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D63" s="36"/>
-      <c r="E63" s="36"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="39"/>
-      <c r="I63" s="40"/>
-      <c r="J63" s="41"/>
-      <c r="K63" s="41"/>
-      <c r="L63" s="41"/>
-      <c r="M63" s="41"/>
-      <c r="N63" s="41"/>
-      <c r="O63" s="41"/>
-      <c r="P63" s="41"/>
-      <c r="Q63" s="41"/>
-      <c r="R63" s="41"/>
-      <c r="S63" s="41"/>
-      <c r="T63" s="41"/>
-      <c r="U63" s="41"/>
-      <c r="V63" s="41"/>
-      <c r="W63" s="41"/>
+      <c r="A63" s="44"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63" s="38"/>
+      <c r="E63" s="38"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="40"/>
+      <c r="H63" s="41"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="43"/>
+      <c r="K63" s="43"/>
+      <c r="L63" s="43"/>
+      <c r="M63" s="43"/>
+      <c r="N63" s="43"/>
+      <c r="O63" s="43"/>
+      <c r="P63" s="43"/>
+      <c r="Q63" s="43"/>
+      <c r="R63" s="43"/>
+      <c r="S63" s="43"/>
+      <c r="T63" s="43"/>
+      <c r="U63" s="43"/>
+      <c r="V63" s="43"/>
+      <c r="W63" s="43"/>
     </row>
     <row r="64" ht="18.75" customHeight="1">
-      <c r="A64" s="42"/>
-      <c r="B64" s="34"/>
-      <c r="C64" s="43"/>
-      <c r="D64" s="36"/>
-      <c r="E64" s="36"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="39"/>
-      <c r="I64" s="40"/>
-      <c r="J64" s="41"/>
-      <c r="K64" s="41"/>
-      <c r="L64" s="41"/>
-      <c r="M64" s="41"/>
-      <c r="N64" s="41"/>
-      <c r="O64" s="41"/>
-      <c r="P64" s="41"/>
-      <c r="Q64" s="41"/>
-      <c r="R64" s="41"/>
-      <c r="S64" s="41"/>
-      <c r="T64" s="41"/>
-      <c r="U64" s="41"/>
-      <c r="V64" s="41"/>
-      <c r="W64" s="41"/>
+      <c r="A64" s="44"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="45"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="39"/>
+      <c r="G64" s="40"/>
+      <c r="H64" s="41"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="43"/>
+      <c r="K64" s="43"/>
+      <c r="L64" s="43"/>
+      <c r="M64" s="43"/>
+      <c r="N64" s="43"/>
+      <c r="O64" s="43"/>
+      <c r="P64" s="43"/>
+      <c r="Q64" s="43"/>
+      <c r="R64" s="43"/>
+      <c r="S64" s="43"/>
+      <c r="T64" s="43"/>
+      <c r="U64" s="43"/>
+      <c r="V64" s="43"/>
+      <c r="W64" s="43"/>
     </row>
     <row r="65" ht="18.75" customHeight="1">
-      <c r="A65" s="42"/>
-      <c r="B65" s="34"/>
-      <c r="C65" s="43"/>
-      <c r="D65" s="36"/>
-      <c r="E65" s="36"/>
-      <c r="F65" s="37"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="39"/>
-      <c r="I65" s="40"/>
-      <c r="J65" s="41"/>
-      <c r="K65" s="41"/>
-      <c r="L65" s="41"/>
-      <c r="M65" s="41"/>
-      <c r="N65" s="41"/>
-      <c r="O65" s="41"/>
-      <c r="P65" s="41"/>
-      <c r="Q65" s="41"/>
-      <c r="R65" s="41"/>
-      <c r="S65" s="41"/>
-      <c r="T65" s="41"/>
-      <c r="U65" s="41"/>
-      <c r="V65" s="41"/>
-      <c r="W65" s="41"/>
+      <c r="A65" s="44"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="45"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="38"/>
+      <c r="F65" s="39"/>
+      <c r="G65" s="40"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="42"/>
+      <c r="J65" s="43"/>
+      <c r="K65" s="43"/>
+      <c r="L65" s="43"/>
+      <c r="M65" s="43"/>
+      <c r="N65" s="43"/>
+      <c r="O65" s="43"/>
+      <c r="P65" s="43"/>
+      <c r="Q65" s="43"/>
+      <c r="R65" s="43"/>
+      <c r="S65" s="43"/>
+      <c r="T65" s="43"/>
+      <c r="U65" s="43"/>
+      <c r="V65" s="43"/>
+      <c r="W65" s="43"/>
     </row>
     <row r="66" ht="18.75" customHeight="1">
-      <c r="A66" s="42"/>
-      <c r="B66" s="34"/>
-      <c r="C66" s="43"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="38"/>
-      <c r="H66" s="39"/>
-      <c r="I66" s="40"/>
-      <c r="J66" s="41"/>
-      <c r="K66" s="41"/>
-      <c r="L66" s="41"/>
-      <c r="M66" s="41"/>
-      <c r="N66" s="41"/>
-      <c r="O66" s="41"/>
-      <c r="P66" s="41"/>
-      <c r="Q66" s="41"/>
-      <c r="R66" s="41"/>
-      <c r="S66" s="41"/>
-      <c r="T66" s="41"/>
-      <c r="U66" s="41"/>
-      <c r="V66" s="41"/>
-      <c r="W66" s="41"/>
+      <c r="A66" s="44"/>
+      <c r="B66" s="36"/>
+      <c r="C66" s="45"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="38"/>
+      <c r="F66" s="39"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="41"/>
+      <c r="I66" s="42"/>
+      <c r="J66" s="43"/>
+      <c r="K66" s="43"/>
+      <c r="L66" s="43"/>
+      <c r="M66" s="43"/>
+      <c r="N66" s="43"/>
+      <c r="O66" s="43"/>
+      <c r="P66" s="43"/>
+      <c r="Q66" s="43"/>
+      <c r="R66" s="43"/>
+      <c r="S66" s="43"/>
+      <c r="T66" s="43"/>
+      <c r="U66" s="43"/>
+      <c r="V66" s="43"/>
+      <c r="W66" s="43"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="42"/>
-      <c r="B67" s="34"/>
-      <c r="C67" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D67" s="36"/>
-      <c r="E67" s="36"/>
-      <c r="F67" s="37"/>
-      <c r="G67" s="38"/>
-      <c r="H67" s="39"/>
-      <c r="I67" s="40"/>
-      <c r="J67" s="41"/>
-      <c r="K67" s="41"/>
-      <c r="L67" s="41"/>
-      <c r="M67" s="41"/>
-      <c r="N67" s="41"/>
-      <c r="O67" s="41"/>
-      <c r="P67" s="41"/>
-      <c r="Q67" s="41"/>
-      <c r="R67" s="41"/>
-      <c r="S67" s="41"/>
-      <c r="T67" s="41"/>
-      <c r="U67" s="41"/>
-      <c r="V67" s="41"/>
-      <c r="W67" s="41"/>
+      <c r="A67" s="44"/>
+      <c r="B67" s="36"/>
+      <c r="C67" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67" s="38"/>
+      <c r="E67" s="38"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="40"/>
+      <c r="H67" s="41"/>
+      <c r="I67" s="42"/>
+      <c r="J67" s="43"/>
+      <c r="K67" s="43"/>
+      <c r="L67" s="43"/>
+      <c r="M67" s="43"/>
+      <c r="N67" s="43"/>
+      <c r="O67" s="43"/>
+      <c r="P67" s="43"/>
+      <c r="Q67" s="43"/>
+      <c r="R67" s="43"/>
+      <c r="S67" s="43"/>
+      <c r="T67" s="43"/>
+      <c r="U67" s="43"/>
+      <c r="V67" s="43"/>
+      <c r="W67" s="43"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="42"/>
-      <c r="B68" s="34"/>
-      <c r="C68" s="43"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="38"/>
-      <c r="H68" s="39"/>
-      <c r="I68" s="40"/>
-      <c r="J68" s="41"/>
-      <c r="K68" s="41"/>
-      <c r="L68" s="41"/>
-      <c r="M68" s="41"/>
-      <c r="N68" s="41"/>
-      <c r="O68" s="41"/>
-      <c r="P68" s="41"/>
-      <c r="Q68" s="41"/>
-      <c r="R68" s="41"/>
-      <c r="S68" s="41"/>
-      <c r="T68" s="41"/>
-      <c r="U68" s="41"/>
-      <c r="V68" s="41"/>
-      <c r="W68" s="41"/>
+      <c r="A68" s="44"/>
+      <c r="B68" s="36"/>
+      <c r="C68" s="45"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="40"/>
+      <c r="H68" s="41"/>
+      <c r="I68" s="42"/>
+      <c r="J68" s="43"/>
+      <c r="K68" s="43"/>
+      <c r="L68" s="43"/>
+      <c r="M68" s="43"/>
+      <c r="N68" s="43"/>
+      <c r="O68" s="43"/>
+      <c r="P68" s="43"/>
+      <c r="Q68" s="43"/>
+      <c r="R68" s="43"/>
+      <c r="S68" s="43"/>
+      <c r="T68" s="43"/>
+      <c r="U68" s="43"/>
+      <c r="V68" s="43"/>
+      <c r="W68" s="43"/>
     </row>
     <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="42"/>
-      <c r="B69" s="34"/>
-      <c r="C69" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="38"/>
-      <c r="H69" s="39"/>
-      <c r="I69" s="40"/>
-      <c r="J69" s="41"/>
-      <c r="K69" s="41"/>
-      <c r="L69" s="41"/>
-      <c r="M69" s="41"/>
-      <c r="N69" s="41"/>
-      <c r="O69" s="41"/>
-      <c r="P69" s="41"/>
-      <c r="Q69" s="41"/>
-      <c r="R69" s="41"/>
-      <c r="S69" s="41"/>
-      <c r="T69" s="41"/>
-      <c r="U69" s="41"/>
-      <c r="V69" s="41"/>
-      <c r="W69" s="41"/>
+      <c r="A69" s="44"/>
+      <c r="B69" s="36"/>
+      <c r="C69" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D69" s="38"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="40"/>
+      <c r="H69" s="41"/>
+      <c r="I69" s="42"/>
+      <c r="J69" s="43"/>
+      <c r="K69" s="43"/>
+      <c r="L69" s="43"/>
+      <c r="M69" s="43"/>
+      <c r="N69" s="43"/>
+      <c r="O69" s="43"/>
+      <c r="P69" s="43"/>
+      <c r="Q69" s="43"/>
+      <c r="R69" s="43"/>
+      <c r="S69" s="43"/>
+      <c r="T69" s="43"/>
+      <c r="U69" s="43"/>
+      <c r="V69" s="43"/>
+      <c r="W69" s="43"/>
     </row>
     <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="45"/>
-      <c r="B70" s="46"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="49"/>
-      <c r="G70" s="49"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="50"/>
-      <c r="J70" s="50"/>
-      <c r="K70" s="50"/>
-      <c r="L70" s="50"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="49"/>
+      <c r="D70" s="50"/>
+      <c r="E70" s="50"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="50"/>
+      <c r="I70" s="52"/>
+      <c r="J70" s="52"/>
+      <c r="K70" s="52"/>
+      <c r="L70" s="52"/>
     </row>
     <row r="72" ht="53.25" customHeight="1"/>
     <row r="73" ht="42" customHeight="1"/>
@@ -5061,43 +5115,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00DD001C-0050-4DBD-9A2A-005E006A0065}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{007C00E2-00AE-41F2-9C53-007E00990092}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>Team</xm:f>
           </x14:formula1>
           <xm:sqref>F107:F65536</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00D100B2-006D-488B-ACC9-000900F50020}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{003D00D7-003D-4D86-A5F0-001400A300C2}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>Category</xm:f>
           </x14:formula1>
           <xm:sqref>G107:G65536</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{003E0052-0094-48FC-99DD-005200EC009E}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00B500B0-0090-4D44-AB04-003900250020}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"Build, Unit Test, System Test, Coding, General , Integration"</xm:f>
           </x14:formula1>
           <xm:sqref>G70</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{001600D4-004F-4D63-9975-000C008A00F5}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{001800DC-0004-448E-8A9B-0068001F002D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>Status</xm:f>
           </x14:formula1>
           <xm:sqref>H107:H65536 H70</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00ED0088-00B1-46E3-B806-0039004E00D1}" type="decimal" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="lessThanOrEqual" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{004F008D-0008-406A-9B33-00A4006700CC}" type="decimal" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="lessThanOrEqual" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>I5</xm:f>
           </x14:formula1>
           <xm:sqref>M26:Q69 J5:J9 J26:L70 K5:L8 L9 R5:W69 M5:Q9 I10:Q22</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{007E00AF-00CE-41F6-98E8-0092007900F2}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{0075003B-009E-4201-A73D-00EF002500C5}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1- Not Started, 2- In Progress, 3- Completed"</xm:f>
           </x14:formula1>
           <xm:sqref>F10:F22 H5:H69</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00260000-003E-4EE9-88D6-0003009300A9}" type="decimal" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{005B0020-00DE-4920-B9A1-00D400570043}" type="decimal" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>0</xm:f>
           </x14:formula1>
@@ -5106,7 +5160,7 @@
           </x14:formula2>
           <xm:sqref>I26:I69 I5:I8</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00680025-009E-4A5E-A06F-002C00E7005E}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{000500BA-0073-4EBA-BA38-00DE004E0056}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"Build, Coding, Design, Integration Test, Regression Test, System Test, Unit Test, Others"</xm:f>
           </x14:formula1>
@@ -5132,77 +5186,77 @@
   </cols>
   <sheetData>
     <row r="1" ht="49.5" customHeight="1">
-      <c r="A1" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
+      <c r="A1" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
     </row>
     <row r="2" ht="26.399999999999999">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="53" t="s">
-        <v>83</v>
+      <c r="B2" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="3" ht="13.199999999999999">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
     </row>
     <row r="4" ht="13.199999999999999">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
     </row>
     <row r="5" ht="13.199999999999999">
-      <c r="A5" s="54"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
+      <c r="A5" s="56"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
     </row>
     <row r="6" ht="13.199999999999999">
-      <c r="A6" s="54"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
+      <c r="A6" s="56"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
     </row>
     <row r="7" ht="13.199999999999999">
-      <c r="A7" s="54"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
+      <c r="A7" s="56"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
     </row>
     <row r="8" ht="13.199999999999999">
-      <c r="A8" s="54"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
     </row>
     <row r="9" ht="13.199999999999999">
-      <c r="A9" s="54"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -5220,161 +5274,161 @@
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.1093799999999998" defaultRowHeight="13.199999999999999" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="55" width="6.8867200000000004"/>
-    <col customWidth="1" min="2" max="4" style="56" width="12.332000000000001"/>
-    <col customWidth="1" min="5" max="5" style="55" width="20.332000000000001"/>
-    <col customWidth="1" min="6" max="6" style="56" width="12.332000000000001"/>
-    <col customWidth="1" min="7" max="7" style="57" width="27.332000000000001"/>
-    <col customWidth="1" min="8" max="8" style="55" width="16.441400000000002"/>
-    <col customWidth="1" min="9" max="9" style="55" width="18.109400000000001"/>
-    <col customWidth="1" min="10" max="257" style="55" width="9.1093799999999998"/>
+    <col customWidth="1" min="1" max="1" style="57" width="6.8867200000000004"/>
+    <col customWidth="1" min="2" max="4" style="58" width="12.332000000000001"/>
+    <col customWidth="1" min="5" max="5" style="57" width="20.332000000000001"/>
+    <col customWidth="1" min="6" max="6" style="58" width="12.332000000000001"/>
+    <col customWidth="1" min="7" max="7" style="59" width="27.332000000000001"/>
+    <col customWidth="1" min="8" max="8" style="57" width="16.441400000000002"/>
+    <col customWidth="1" min="9" max="9" style="57" width="18.109400000000001"/>
+    <col customWidth="1" min="10" max="257" style="57" width="9.1093799999999998"/>
   </cols>
   <sheetData>
-    <row r="1" s="58" customFormat="1" ht="45.75" customHeight="1">
-      <c r="A1" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="59" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" s="59" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" s="59" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="59" t="s">
+    <row r="1" s="60" customFormat="1" ht="45.75" customHeight="1">
+      <c r="A1" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="B1" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="C1" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="D1" s="61" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" s="55" customFormat="1" ht="38.25">
-      <c r="A2" s="60">
+      <c r="E1" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="61" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" s="57" customFormat="1" ht="38.25">
+      <c r="A2" s="62">
         <v>1</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="60" t="s">
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="G2" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="H2" s="60" t="s">
-        <v>95</v>
-      </c>
-      <c r="I2" s="60" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" s="55" customFormat="1">
-      <c r="A3" s="62">
+      <c r="F2" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="I2" s="62" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" s="57" customFormat="1">
+      <c r="A3" s="64">
         <v>2</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="60" t="s">
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-    </row>
-    <row r="4" s="55" customFormat="1">
-      <c r="A4" s="62">
+      <c r="F3" s="64"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+    </row>
+    <row r="4" s="57" customFormat="1">
+      <c r="A4" s="64">
         <v>3</v>
       </c>
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="60" t="s">
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="62"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-    </row>
-    <row r="5" s="55" customFormat="1">
-      <c r="A5" s="62">
+      <c r="F4" s="64"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+    </row>
+    <row r="5" s="57" customFormat="1">
+      <c r="A5" s="64">
         <v>4</v>
       </c>
-      <c r="B5" s="60" t="s">
+      <c r="B5" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="65">
+      <c r="C5" s="64"/>
+      <c r="D5" s="67">
         <v>46063</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="62"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-    </row>
-    <row r="6" s="55" customFormat="1">
-      <c r="A6" s="62">
+      <c r="F5" s="64"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+    </row>
+    <row r="6" s="57" customFormat="1">
+      <c r="A6" s="64">
         <v>5</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-    </row>
-    <row r="7" s="55" customFormat="1">
-      <c r="A7" s="62">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+    </row>
+    <row r="7" s="57" customFormat="1">
+      <c r="A7" s="64">
         <v>6</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-    </row>
-    <row r="8" s="55" customFormat="1">
-      <c r="A8" s="62">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+    </row>
+    <row r="8" s="57" customFormat="1">
+      <c r="A8" s="64">
         <v>7</v>
       </c>
-      <c r="B8" s="62"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/docs/Internship_artifacts/Agile_Template_v0.1.xlsx
+++ b/docs/Internship_artifacts/Agile_Template_v0.1.xlsx
@@ -4,7 +4,7 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="0"/>
   <workbookProtection lockStructure="0" lockWindows="0" workbookPassword="0000"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="1" state="visible" r:id="rId2"/>
@@ -457,7 +457,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <t xml:space="preserve">Planned Sprint</t>
   </si>
@@ -751,31 +751,18 @@
   </si>
   <si>
     <t xml:space="preserve">Action taken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Break tasks into smaller units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">add only applicable code commits, note all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily code commits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Created task-level checklist</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="[$-1009]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="169" formatCode="dd-mmm-yy"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -1535,7 +1522,7 @@
     <xf fontId="19" fillId="0" borderId="9" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="20" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1750,9 +1737,6 @@
     </xf>
     <xf fontId="14" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="14" fillId="0" borderId="10" numFmtId="169" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="31" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1829,7 +1813,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Sumeet Kumar Barua08" id="{E342A5D8-9227-19F5-C930-935878CACE1A}"/>
+  <person displayName="Sumeet Kumar Barua08" id="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}"/>
 </personList>
 </file>
 
@@ -2338,7 +2322,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="F1" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00AF0084-0059-46C3-AA99-008E004D0035}" done="0">
+  <threadedComment ref="F1" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{00AF0084-0059-46C3-AA99-008E004D0035}" done="0">
     <text xml:space="preserve">Mention the US ID(s) on which the user story depends.
 </text>
   </threadedComment>
@@ -2347,75 +2331,75 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D2" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00F800F9-00F5-4EEB-A626-00AC003800DC}" done="0">
+  <threadedComment ref="D2" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{00F800F9-00F5-4EEB-A626-00AC003800DC}" done="0">
     <text xml:space="preserve">Please enter the dates in either of these formats: 
 9/15/2016  or
 15-Sep-2016
 </text>
   </threadedComment>
-  <threadedComment ref="E2" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{000200F9-001E-4BFA-B542-00FB000F008B}" done="0">
+  <threadedComment ref="E2" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{000200F9-001E-4BFA-B542-00FB000F008B}" done="0">
     <text xml:space="preserve">Please enter the dates in either of these formats: 
 9/15/2016  or
 15-Sep-2016
 </text>
   </threadedComment>
-  <threadedComment ref="K3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00A900BC-0098-4ADA-991F-004100B900CA}" done="0">
+  <threadedComment ref="K3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{00A900BC-0098-4ADA-991F-004100B900CA}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 2 work
 </text>
   </threadedComment>
-  <threadedComment ref="L3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{007E003B-0039-4F19-8B63-00C500F60085}" done="0">
+  <threadedComment ref="L3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{007E003B-0039-4F19-8B63-00C500F60085}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 3 work
 </text>
   </threadedComment>
-  <threadedComment ref="M3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{004500B6-006E-4D69-9AA8-00D500D5008B}" done="0">
+  <threadedComment ref="M3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{004500B6-006E-4D69-9AA8-00D500D5008B}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 4 work
 </text>
   </threadedComment>
-  <threadedComment ref="N3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{0076002F-00B4-461E-96FC-0042003D000F}" done="0">
+  <threadedComment ref="N3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{0076002F-00B4-461E-96FC-0042003D000F}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 5 work
 </text>
   </threadedComment>
-  <threadedComment ref="O3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00BD00ED-0020-4FB3-8E63-00DF0065002A}" done="0">
+  <threadedComment ref="O3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{00BD00ED-0020-4FB3-8E63-00DF0065002A}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 6 work
 </text>
   </threadedComment>
-  <threadedComment ref="P3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{007A00FA-00D7-4145-9950-0006005B0057}" done="0">
+  <threadedComment ref="P3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{007A00FA-00D7-4145-9950-0006005B0057}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 7 work
 </text>
   </threadedComment>
-  <threadedComment ref="Q3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{004100A5-0097-4D17-B730-0012008100F5}" done="0">
+  <threadedComment ref="Q3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{004100A5-0097-4D17-B730-0012008100F5}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 8 work
 </text>
   </threadedComment>
-  <threadedComment ref="R3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{005B0000-002C-4B0C-BADE-00E6000B00C9}" done="0">
+  <threadedComment ref="R3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{005B0000-002C-4B0C-BADE-00E6000B00C9}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 9 work
 </text>
   </threadedComment>
-  <threadedComment ref="S3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00430062-00FB-4330-872F-006500830079}" done="0">
+  <threadedComment ref="S3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{00430062-00FB-4330-872F-006500830079}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 10 work
 </text>
   </threadedComment>
-  <threadedComment ref="T3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{002900E7-007B-4830-9B69-00F800460012}" done="0">
+  <threadedComment ref="T3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{002900E7-007B-4830-9B69-00F800460012}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 11 work
 </text>
   </threadedComment>
-  <threadedComment ref="U3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{007300EB-00B7-41DD-AFC5-000B00040082}" done="0">
+  <threadedComment ref="U3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{007300EB-00B7-41DD-AFC5-000B00040082}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 12 work
 </text>
   </threadedComment>
-  <threadedComment ref="V3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00370093-00CE-47AD-A1F0-00900043001F}" done="0">
+  <threadedComment ref="V3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{00370093-00CE-47AD-A1F0-00900043001F}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 13 work
 </text>
   </threadedComment>
-  <threadedComment ref="W3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{00C30045-0073-4B39-B18E-007A00DC001F}" done="0">
+  <threadedComment ref="W3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{00C30045-0073-4B39-B18E-007A00DC001F}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 14 work
 </text>
   </threadedComment>
-  <threadedComment ref="I3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{0015002A-006D-42C0-8CB5-0043007D001D}" done="0">
+  <threadedComment ref="I3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{0015002A-006D-42C0-8CB5-0043007D001D}" done="0">
     <text xml:space="preserve">This is the total task estimated in hours for all the user stories 
 </text>
   </threadedComment>
-  <threadedComment ref="J3" personId="{E342A5D8-9227-19F5-C930-935878CACE1A}" id="{006300B3-0017-43A3-AC6F-00670025009B}" done="0">
+  <threadedComment ref="J3" personId="{4F8F2A97-6DAE-0994-DD2E-7E15B5989538}" id="{006300B3-0017-43A3-AC6F-00670025009B}" done="0">
     <text xml:space="preserve">Pending effort hours after completion of day 1 work
 </text>
   </threadedComment>
@@ -3127,13 +3111,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00D300BE-00D9-4AF6-99A1-009F000800B6}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00C300E7-0038-4480-B20A-0019007A0080}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1- Not Started, 2- In Progress, 3- Completed"</xm:f>
           </x14:formula1>
           <xm:sqref>H2:H12 H15 H16:H44 H13 H14</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{007200A6-001E-464A-BA1B-00FE005800F6}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{0087000B-00E0-45E2-9AC3-00A000FD0028}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"MUST HAVE, SHOULD HAVE, COULD HAVE, WON'T HAVE"</xm:f>
           </x14:formula1>
@@ -5115,43 +5099,43 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8" disablePrompts="0">
-        <x14:dataValidation xr:uid="{007C00E2-00AE-41F2-9C53-007E00990092}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{005000BA-00D5-4E55-94BE-003300E300C6}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>Team</xm:f>
           </x14:formula1>
           <xm:sqref>F107:F65536</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{003D00D7-003D-4D86-A5F0-001400A300C2}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{000B0024-00DD-476F-AF9E-00700076006B}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>Category</xm:f>
           </x14:formula1>
           <xm:sqref>G107:G65536</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00B500B0-0090-4D44-AB04-003900250020}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{009B007F-0011-45A6-9CBB-00BB001700CD}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"Build, Unit Test, System Test, Coding, General , Integration"</xm:f>
           </x14:formula1>
           <xm:sqref>G70</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{001800DC-0004-448E-8A9B-0068001F002D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00550081-005E-4AD6-93A1-00B900B700C6}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>Status</xm:f>
           </x14:formula1>
           <xm:sqref>H107:H65536 H70</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{004F008D-0008-406A-9B33-00A4006700CC}" type="decimal" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="lessThanOrEqual" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{008300E9-0005-48BE-8691-00D5005F00D2}" type="decimal" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="lessThanOrEqual" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>I5</xm:f>
           </x14:formula1>
           <xm:sqref>M26:Q69 J5:J9 J26:L70 K5:L8 L9 R5:W69 M5:Q9 I10:Q22</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{0075003B-009E-4201-A73D-00EF002500C5}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00E500F6-001C-4383-A6FC-00BE00AA0095}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1- Not Started, 2- In Progress, 3- Completed"</xm:f>
           </x14:formula1>
           <xm:sqref>F10:F22 H5:H69</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{005B0020-00DE-4920-B9A1-00D400570043}" type="decimal" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{002C00EE-000C-442B-BA0E-00E700460053}" type="decimal" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>0</xm:f>
           </x14:formula1>
@@ -5160,7 +5144,7 @@
           </x14:formula2>
           <xm:sqref>I26:I69 I5:I8</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{000500BA-0073-4EBA-BA38-00DE004E0056}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{007D0098-0011-4B23-BD21-000500760077}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"Build, Coding, Design, Integration Test, Regression Test, System Test, Unit Test, Others"</xm:f>
           </x14:formula1>
@@ -5320,23 +5304,19 @@
       <c r="B2" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
+      <c r="C2" s="63">
+        <v>46020</v>
+      </c>
+      <c r="D2" s="63">
+        <v>46034</v>
+      </c>
       <c r="E2" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="62" t="s">
-        <v>98</v>
-      </c>
-      <c r="G2" s="62" t="s">
-        <v>99</v>
-      </c>
-      <c r="H2" s="62" t="s">
-        <v>100</v>
-      </c>
-      <c r="I2" s="62" t="s">
-        <v>101</v>
-      </c>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
     </row>
     <row r="3" s="57" customFormat="1">
       <c r="A3" s="64">
@@ -5345,8 +5325,12 @@
       <c r="B3" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
+      <c r="C3" s="63">
+        <v>46035</v>
+      </c>
+      <c r="D3" s="63">
+        <v>46049</v>
+      </c>
       <c r="E3" s="62" t="s">
         <v>13</v>
       </c>
@@ -5362,8 +5346,12 @@
       <c r="B4" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
+      <c r="C4" s="63">
+        <v>46050</v>
+      </c>
+      <c r="D4" s="63">
+        <v>46064</v>
+      </c>
       <c r="E4" s="62" t="s">
         <v>13</v>
       </c>
@@ -5379,15 +5367,17 @@
       <c r="B5" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="67">
-        <v>46063</v>
+      <c r="C5" s="63">
+        <v>46065</v>
+      </c>
+      <c r="D5" s="63">
+        <v>46079</v>
       </c>
       <c r="E5" s="62" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="64"/>
-      <c r="G5" s="68"/>
+      <c r="G5" s="67"/>
       <c r="H5" s="66"/>
       <c r="I5" s="66"/>
     </row>
@@ -5400,7 +5390,7 @@
       <c r="D6" s="64"/>
       <c r="E6" s="66"/>
       <c r="F6" s="64"/>
-      <c r="G6" s="69"/>
+      <c r="G6" s="68"/>
       <c r="H6" s="66"/>
       <c r="I6" s="66"/>
     </row>
@@ -5426,7 +5416,7 @@
       <c r="D8" s="64"/>
       <c r="E8" s="66"/>
       <c r="F8" s="64"/>
-      <c r="G8" s="69"/>
+      <c r="G8" s="68"/>
       <c r="H8" s="66"/>
       <c r="I8" s="66"/>
     </row>
